--- a/LangMod/EN/Zones.xlsx
+++ b/LangMod/EN/Zones.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Zone" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Zone!$A$3:$D$34</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Zone!$A$3:$D$36</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="131">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -678,6 +678,12 @@
     <t xml:space="preserve">Study Hall</t>
   </si>
   <si>
+    <t xml:space="preserve">instance_road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance_mofuroad</t>
+  </si>
+  <si>
     <t xml:space="preserve">instance_guild_merchant</t>
   </si>
   <si>
@@ -1013,7 +1019,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">NefiaWater</t>
+      <t xml:space="preserve">NefiWater</t>
     </r>
   </si>
   <si>
@@ -1300,37 +1306,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
@@ -1469,7 +1475,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD34"/>
+  <dimension ref="A1:XFD36"/>
   <sheetFormatPr defaultColWidth="14.43359375" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.97"/>
@@ -1483,7 +1489,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16336" style="1" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1653,7 +1659,7 @@
       <c r="V3" s="4"/>
       <c r="W3" s="4"/>
     </row>
-    <row r="4" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
@@ -1741,7 +1747,7 @@
       <c r="XFC4" s="1"/>
       <c r="XFD4" s="1"/>
     </row>
-    <row r="5" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>35</v>
       </c>
@@ -1828,7 +1834,7 @@
       <c r="XFC5" s="1"/>
       <c r="XFD5" s="1"/>
     </row>
-    <row r="6" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>37</v>
       </c>
@@ -1915,7 +1921,7 @@
       <c r="XFC6" s="1"/>
       <c r="XFD6" s="1"/>
     </row>
-    <row r="7" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>39</v>
       </c>
@@ -2002,7 +2008,7 @@
       <c r="XFC7" s="1"/>
       <c r="XFD7" s="1"/>
     </row>
-    <row r="8" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>41</v>
       </c>
@@ -2089,7 +2095,7 @@
       <c r="XFC8" s="1"/>
       <c r="XFD8" s="1"/>
     </row>
-    <row r="9" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
         <v>43</v>
       </c>
@@ -2176,7 +2182,7 @@
       <c r="XFC9" s="1"/>
       <c r="XFD9" s="1"/>
     </row>
-    <row r="10" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
         <v>45</v>
       </c>
@@ -2263,7 +2269,7 @@
       <c r="XFC10" s="1"/>
       <c r="XFD10" s="1"/>
     </row>
-    <row r="11" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
         <v>47</v>
       </c>
@@ -2350,7 +2356,7 @@
       <c r="XFC11" s="1"/>
       <c r="XFD11" s="1"/>
     </row>
-    <row r="12" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
         <v>49</v>
       </c>
@@ -2437,7 +2443,7 @@
       <c r="XFC12" s="1"/>
       <c r="XFD12" s="1"/>
     </row>
-    <row r="13" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
         <v>51</v>
       </c>
@@ -2524,7 +2530,7 @@
       <c r="XFC13" s="1"/>
       <c r="XFD13" s="1"/>
     </row>
-    <row r="14" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
         <v>53</v>
       </c>
@@ -2611,7 +2617,7 @@
       <c r="XFC14" s="1"/>
       <c r="XFD14" s="1"/>
     </row>
-    <row r="15" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
         <v>55</v>
       </c>
@@ -2698,7 +2704,7 @@
       <c r="XFC15" s="1"/>
       <c r="XFD15" s="1"/>
     </row>
-    <row r="16" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
         <v>57</v>
       </c>
@@ -2785,7 +2791,7 @@
       <c r="XFC16" s="1"/>
       <c r="XFD16" s="1"/>
     </row>
-    <row r="17" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
         <v>59</v>
       </c>
@@ -2872,7 +2878,7 @@
       <c r="XFC17" s="1"/>
       <c r="XFD17" s="1"/>
     </row>
-    <row r="18" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
         <v>61</v>
       </c>
@@ -2959,7 +2965,7 @@
       <c r="XFC18" s="1"/>
       <c r="XFD18" s="1"/>
     </row>
-    <row r="19" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
         <v>63</v>
       </c>
@@ -3046,7 +3052,7 @@
       <c r="XFC19" s="1"/>
       <c r="XFD19" s="1"/>
     </row>
-    <row r="20" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
         <v>65</v>
       </c>
@@ -3133,7 +3139,7 @@
       <c r="XFC20" s="1"/>
       <c r="XFD20" s="1"/>
     </row>
-    <row r="21" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
         <v>69</v>
       </c>
@@ -3220,16 +3226,15 @@
       <c r="XFC21" s="1"/>
       <c r="XFD21" s="1"/>
     </row>
-    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
+    <row r="22" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>74</v>
+      <c r="C22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>31</v>
@@ -3240,20 +3245,15 @@
       <c r="G22" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="H22" s="4"/>
       <c r="I22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4" t="s">
-        <v>75</v>
+      <c r="K22" s="6" t="s">
+        <v>72</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
       <c r="P22" s="2" t="n">
         <v>0</v>
       </c>
@@ -3263,22 +3263,65 @@
       <c r="R22" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="S22" s="4"/>
-      <c r="T22" s="4"/>
-      <c r="U22" s="4"/>
-      <c r="V22" s="4"/>
-      <c r="W22" s="4"/>
+      <c r="XDH22" s="1"/>
+      <c r="XDI22" s="1"/>
+      <c r="XDJ22" s="1"/>
+      <c r="XDK22" s="1"/>
+      <c r="XDL22" s="1"/>
+      <c r="XDM22" s="1"/>
+      <c r="XDN22" s="1"/>
+      <c r="XDO22" s="1"/>
+      <c r="XDP22" s="1"/>
+      <c r="XDQ22" s="1"/>
+      <c r="XDR22" s="1"/>
+      <c r="XDS22" s="1"/>
+      <c r="XDT22" s="1"/>
+      <c r="XDU22" s="1"/>
+      <c r="XDV22" s="1"/>
+      <c r="XDW22" s="1"/>
+      <c r="XDX22" s="1"/>
+      <c r="XDY22" s="1"/>
+      <c r="XDZ22" s="1"/>
+      <c r="XEA22" s="1"/>
+      <c r="XEB22" s="1"/>
+      <c r="XEC22" s="1"/>
+      <c r="XED22" s="1"/>
+      <c r="XEE22" s="1"/>
+      <c r="XEF22" s="1"/>
+      <c r="XEG22" s="1"/>
+      <c r="XEH22" s="1"/>
+      <c r="XEI22" s="1"/>
+      <c r="XEJ22" s="1"/>
+      <c r="XEK22" s="1"/>
+      <c r="XEL22" s="1"/>
+      <c r="XEM22" s="1"/>
+      <c r="XEN22" s="1"/>
+      <c r="XEO22" s="1"/>
+      <c r="XEP22" s="1"/>
+      <c r="XEQ22" s="1"/>
+      <c r="XER22" s="1"/>
+      <c r="XES22" s="1"/>
+      <c r="XET22" s="1"/>
+      <c r="XEU22" s="1"/>
+      <c r="XEV22" s="1"/>
+      <c r="XEW22" s="1"/>
+      <c r="XEX22" s="1"/>
+      <c r="XEY22" s="1"/>
+      <c r="XEZ22" s="1"/>
+      <c r="XFA22" s="1"/>
+      <c r="XFB22" s="1"/>
+      <c r="XFC22" s="1"/>
+      <c r="XFD22" s="1"/>
     </row>
-    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>78</v>
+    <row r="23" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>31</v>
@@ -3289,20 +3332,15 @@
       <c r="G23" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="H23" s="4"/>
       <c r="I23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4" t="s">
-        <v>79</v>
+      <c r="K23" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="M23" s="4"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="4"/>
       <c r="P23" s="2" t="n">
         <v>0</v>
       </c>
@@ -3312,22 +3350,66 @@
       <c r="R23" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="S23" s="4"/>
-      <c r="T23" s="4"/>
-      <c r="U23" s="4"/>
-      <c r="V23" s="4"/>
-      <c r="W23" s="4"/>
+      <c r="XDH23" s="0"/>
+      <c r="XDI23" s="0"/>
+      <c r="XDJ23" s="0"/>
+      <c r="XDK23" s="0"/>
+      <c r="XDL23" s="0"/>
+      <c r="XDM23" s="0"/>
+      <c r="XDN23" s="0"/>
+      <c r="XDO23" s="0"/>
+      <c r="XDP23" s="0"/>
+      <c r="XDQ23" s="0"/>
+      <c r="XDR23" s="0"/>
+      <c r="XDS23" s="0"/>
+      <c r="XDT23" s="0"/>
+      <c r="XDU23" s="0"/>
+      <c r="XDV23" s="0"/>
+      <c r="XDW23" s="0"/>
+      <c r="XDX23" s="0"/>
+      <c r="XDY23" s="0"/>
+      <c r="XDZ23" s="0"/>
+      <c r="XEA23" s="0"/>
+      <c r="XEB23" s="0"/>
+      <c r="XEC23" s="0"/>
+      <c r="XED23" s="0"/>
+      <c r="XEE23" s="0"/>
+      <c r="XEF23" s="0"/>
+      <c r="XEG23" s="0"/>
+      <c r="XEH23" s="0"/>
+      <c r="XEI23" s="0"/>
+      <c r="XEJ23" s="0"/>
+      <c r="XEK23" s="0"/>
+      <c r="XEL23" s="0"/>
+      <c r="XEM23" s="0"/>
+      <c r="XEN23" s="0"/>
+      <c r="XEO23" s="0"/>
+      <c r="XEP23" s="0"/>
+      <c r="XEQ23" s="0"/>
+      <c r="XER23" s="0"/>
+      <c r="XES23" s="0"/>
+      <c r="XET23" s="0"/>
+      <c r="XEU23" s="0"/>
+      <c r="XEV23" s="0"/>
+      <c r="XEW23" s="0"/>
+      <c r="XEX23" s="0"/>
+      <c r="XEY23" s="0"/>
+      <c r="XEZ23" s="0"/>
+      <c r="XFA23" s="0"/>
+      <c r="XFB23" s="0"/>
+      <c r="XFC23" s="0"/>
+      <c r="XFD23" s="0"/>
     </row>
-    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="s">
-        <v>80</v>
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="4" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>31</v>
@@ -3344,13 +3426,13 @@
       </c>
       <c r="J24" s="4"/>
       <c r="K24" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M24" s="4"/>
-      <c r="N24" s="2"/>
+      <c r="N24" s="4"/>
       <c r="O24" s="4"/>
       <c r="P24" s="2" t="n">
         <v>0</v>
@@ -3367,16 +3449,16 @@
       <c r="V24" s="4"/>
       <c r="W24" s="4"/>
     </row>
-    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="B25" s="4"/>
+        <v>78</v>
+      </c>
+      <c r="B25" s="7"/>
       <c r="C25" s="4" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>31</v>
@@ -3387,20 +3469,20 @@
       <c r="G25" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="H25" s="9"/>
+      <c r="H25" s="4"/>
       <c r="I25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9" t="s">
-        <v>87</v>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="M25" s="9"/>
+      <c r="M25" s="4"/>
       <c r="N25" s="2"/>
-      <c r="O25" s="9"/>
+      <c r="O25" s="4"/>
       <c r="P25" s="2" t="n">
         <v>0</v>
       </c>
@@ -3410,24 +3492,25 @@
       <c r="R25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="S25" s="9"/>
-      <c r="T25" s="9"/>
-      <c r="U25" s="9"/>
-      <c r="V25" s="9"/>
-      <c r="W25" s="9"/>
+      <c r="S25" s="4"/>
+      <c r="T25" s="4"/>
+      <c r="U25" s="4"/>
+      <c r="V25" s="4"/>
+      <c r="W25" s="4"/>
     </row>
-    <row r="26" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>33</v>
+    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>1</v>
@@ -3435,15 +3518,20 @@
       <c r="G26" s="2" t="n">
         <v>100</v>
       </c>
+      <c r="H26" s="4"/>
       <c r="I26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K26" s="6" t="s">
-        <v>91</v>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="M26" s="4"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="4"/>
       <c r="P26" s="2" t="n">
         <v>0</v>
       </c>
@@ -3453,68 +3541,25 @@
       <c r="R26" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="XDH26" s="1"/>
-      <c r="XDI26" s="1"/>
-      <c r="XDJ26" s="1"/>
-      <c r="XDK26" s="1"/>
-      <c r="XDL26" s="1"/>
-      <c r="XDM26" s="1"/>
-      <c r="XDN26" s="1"/>
-      <c r="XDO26" s="1"/>
-      <c r="XDP26" s="1"/>
-      <c r="XDQ26" s="1"/>
-      <c r="XDR26" s="1"/>
-      <c r="XDS26" s="1"/>
-      <c r="XDT26" s="1"/>
-      <c r="XDU26" s="1"/>
-      <c r="XDV26" s="1"/>
-      <c r="XDW26" s="1"/>
-      <c r="XDX26" s="1"/>
-      <c r="XDY26" s="1"/>
-      <c r="XDZ26" s="1"/>
-      <c r="XEA26" s="1"/>
-      <c r="XEB26" s="1"/>
-      <c r="XEC26" s="1"/>
-      <c r="XED26" s="1"/>
-      <c r="XEE26" s="1"/>
-      <c r="XEF26" s="1"/>
-      <c r="XEG26" s="1"/>
-      <c r="XEH26" s="1"/>
-      <c r="XEI26" s="1"/>
-      <c r="XEJ26" s="1"/>
-      <c r="XEK26" s="1"/>
-      <c r="XEL26" s="1"/>
-      <c r="XEM26" s="1"/>
-      <c r="XEN26" s="1"/>
-      <c r="XEO26" s="1"/>
-      <c r="XEP26" s="1"/>
-      <c r="XEQ26" s="1"/>
-      <c r="XER26" s="1"/>
-      <c r="XES26" s="1"/>
-      <c r="XET26" s="1"/>
-      <c r="XEU26" s="1"/>
-      <c r="XEV26" s="1"/>
-      <c r="XEW26" s="1"/>
-      <c r="XEX26" s="1"/>
-      <c r="XEY26" s="1"/>
-      <c r="XEZ26" s="1"/>
-      <c r="XFA26" s="1"/>
-      <c r="XFB26" s="1"/>
-      <c r="XFC26" s="1"/>
-      <c r="XFD26" s="1"/>
+      <c r="S26" s="4"/>
+      <c r="T26" s="4"/>
+      <c r="U26" s="4"/>
+      <c r="V26" s="4"/>
+      <c r="W26" s="4"/>
     </row>
-    <row r="27" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>33</v>
+    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>1</v>
@@ -3522,15 +3567,20 @@
       <c r="G27" s="2" t="n">
         <v>100</v>
       </c>
+      <c r="H27" s="9"/>
       <c r="I27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K27" s="6" t="s">
-        <v>93</v>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9" t="s">
+        <v>89</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="M27" s="9"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="9"/>
       <c r="P27" s="2" t="n">
         <v>0</v>
       </c>
@@ -3540,68 +3590,24 @@
       <c r="R27" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="XDH27" s="1"/>
-      <c r="XDI27" s="1"/>
-      <c r="XDJ27" s="1"/>
-      <c r="XDK27" s="1"/>
-      <c r="XDL27" s="1"/>
-      <c r="XDM27" s="1"/>
-      <c r="XDN27" s="1"/>
-      <c r="XDO27" s="1"/>
-      <c r="XDP27" s="1"/>
-      <c r="XDQ27" s="1"/>
-      <c r="XDR27" s="1"/>
-      <c r="XDS27" s="1"/>
-      <c r="XDT27" s="1"/>
-      <c r="XDU27" s="1"/>
-      <c r="XDV27" s="1"/>
-      <c r="XDW27" s="1"/>
-      <c r="XDX27" s="1"/>
-      <c r="XDY27" s="1"/>
-      <c r="XDZ27" s="1"/>
-      <c r="XEA27" s="1"/>
-      <c r="XEB27" s="1"/>
-      <c r="XEC27" s="1"/>
-      <c r="XED27" s="1"/>
-      <c r="XEE27" s="1"/>
-      <c r="XEF27" s="1"/>
-      <c r="XEG27" s="1"/>
-      <c r="XEH27" s="1"/>
-      <c r="XEI27" s="1"/>
-      <c r="XEJ27" s="1"/>
-      <c r="XEK27" s="1"/>
-      <c r="XEL27" s="1"/>
-      <c r="XEM27" s="1"/>
-      <c r="XEN27" s="1"/>
-      <c r="XEO27" s="1"/>
-      <c r="XEP27" s="1"/>
-      <c r="XEQ27" s="1"/>
-      <c r="XER27" s="1"/>
-      <c r="XES27" s="1"/>
-      <c r="XET27" s="1"/>
-      <c r="XEU27" s="1"/>
-      <c r="XEV27" s="1"/>
-      <c r="XEW27" s="1"/>
-      <c r="XEX27" s="1"/>
-      <c r="XEY27" s="1"/>
-      <c r="XEZ27" s="1"/>
-      <c r="XFA27" s="1"/>
-      <c r="XFB27" s="1"/>
-      <c r="XFC27" s="1"/>
-      <c r="XFD27" s="1"/>
+      <c r="S27" s="9"/>
+      <c r="T27" s="9"/>
+      <c r="U27" s="9"/>
+      <c r="V27" s="9"/>
+      <c r="W27" s="9"/>
     </row>
-    <row r="28" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>1</v>
@@ -3613,12 +3619,11 @@
         <v>0</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O28" s="1"/>
       <c r="P28" s="2" t="n">
         <v>0</v>
       </c>
@@ -3678,112 +3683,193 @@
       <c r="XFC28" s="1"/>
       <c r="XFD28" s="1"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D29" s="1" t="s">
+    <row r="29" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F29" s="1" t="n">
+      <c r="E29" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="I29" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="L29" s="1" t="s">
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="L29" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N29" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="O29" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="P29" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="1" t="s">
+      <c r="P29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="S29" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="XDH29" s="1"/>
+      <c r="XDI29" s="1"/>
+      <c r="XDJ29" s="1"/>
+      <c r="XDK29" s="1"/>
+      <c r="XDL29" s="1"/>
+      <c r="XDM29" s="1"/>
+      <c r="XDN29" s="1"/>
+      <c r="XDO29" s="1"/>
+      <c r="XDP29" s="1"/>
+      <c r="XDQ29" s="1"/>
+      <c r="XDR29" s="1"/>
+      <c r="XDS29" s="1"/>
+      <c r="XDT29" s="1"/>
+      <c r="XDU29" s="1"/>
+      <c r="XDV29" s="1"/>
+      <c r="XDW29" s="1"/>
+      <c r="XDX29" s="1"/>
+      <c r="XDY29" s="1"/>
+      <c r="XDZ29" s="1"/>
+      <c r="XEA29" s="1"/>
+      <c r="XEB29" s="1"/>
+      <c r="XEC29" s="1"/>
+      <c r="XED29" s="1"/>
+      <c r="XEE29" s="1"/>
+      <c r="XEF29" s="1"/>
+      <c r="XEG29" s="1"/>
+      <c r="XEH29" s="1"/>
+      <c r="XEI29" s="1"/>
+      <c r="XEJ29" s="1"/>
+      <c r="XEK29" s="1"/>
+      <c r="XEL29" s="1"/>
+      <c r="XEM29" s="1"/>
+      <c r="XEN29" s="1"/>
+      <c r="XEO29" s="1"/>
+      <c r="XEP29" s="1"/>
+      <c r="XEQ29" s="1"/>
+      <c r="XER29" s="1"/>
+      <c r="XES29" s="1"/>
+      <c r="XET29" s="1"/>
+      <c r="XEU29" s="1"/>
+      <c r="XEV29" s="1"/>
+      <c r="XEW29" s="1"/>
+      <c r="XEX29" s="1"/>
+      <c r="XEY29" s="1"/>
+      <c r="XEZ29" s="1"/>
+      <c r="XFA29" s="1"/>
+      <c r="XFB29" s="1"/>
+      <c r="XFC29" s="1"/>
+      <c r="XFD29" s="1"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="F30" s="1" t="n">
+    <row r="30" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="I30" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="N30" s="1" t="s">
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O30" s="1"/>
+      <c r="P30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="XDH30" s="1"/>
+      <c r="XDI30" s="1"/>
+      <c r="XDJ30" s="1"/>
+      <c r="XDK30" s="1"/>
+      <c r="XDL30" s="1"/>
+      <c r="XDM30" s="1"/>
+      <c r="XDN30" s="1"/>
+      <c r="XDO30" s="1"/>
+      <c r="XDP30" s="1"/>
+      <c r="XDQ30" s="1"/>
+      <c r="XDR30" s="1"/>
+      <c r="XDS30" s="1"/>
+      <c r="XDT30" s="1"/>
+      <c r="XDU30" s="1"/>
+      <c r="XDV30" s="1"/>
+      <c r="XDW30" s="1"/>
+      <c r="XDX30" s="1"/>
+      <c r="XDY30" s="1"/>
+      <c r="XDZ30" s="1"/>
+      <c r="XEA30" s="1"/>
+      <c r="XEB30" s="1"/>
+      <c r="XEC30" s="1"/>
+      <c r="XED30" s="1"/>
+      <c r="XEE30" s="1"/>
+      <c r="XEF30" s="1"/>
+      <c r="XEG30" s="1"/>
+      <c r="XEH30" s="1"/>
+      <c r="XEI30" s="1"/>
+      <c r="XEJ30" s="1"/>
+      <c r="XEK30" s="1"/>
+      <c r="XEL30" s="1"/>
+      <c r="XEM30" s="1"/>
+      <c r="XEN30" s="1"/>
+      <c r="XEO30" s="1"/>
+      <c r="XEP30" s="1"/>
+      <c r="XEQ30" s="1"/>
+      <c r="XER30" s="1"/>
+      <c r="XES30" s="1"/>
+      <c r="XET30" s="1"/>
+      <c r="XEU30" s="1"/>
+      <c r="XEV30" s="1"/>
+      <c r="XEW30" s="1"/>
+      <c r="XEX30" s="1"/>
+      <c r="XEY30" s="1"/>
+      <c r="XEZ30" s="1"/>
+      <c r="XFA30" s="1"/>
+      <c r="XFB30" s="1"/>
+      <c r="XFC30" s="1"/>
+      <c r="XFD30" s="1"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="O30" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="P30" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>1</v>
@@ -3795,16 +3881,16 @@
         <v>0</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="P31" s="1" t="n">
         <v>0</v>
@@ -3816,21 +3902,21 @@
         <v>34</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>116</v>
+        <v>106</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>107</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>1</v>
@@ -3842,16 +3928,16 @@
         <v>0</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="P32" s="1" t="n">
         <v>0</v>
@@ -3863,21 +3949,21 @@
         <v>34</v>
       </c>
       <c r="S32" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>120</v>
+        <v>112</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>1</v>
@@ -3889,16 +3975,16 @@
         <v>0</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="P33" s="1" t="n">
         <v>0</v>
@@ -3910,21 +3996,21 @@
         <v>34</v>
       </c>
       <c r="S33" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>126</v>
+        <v>117</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>1</v>
@@ -3936,16 +4022,16 @@
         <v>0</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="P34" s="1" t="n">
         <v>0</v>
@@ -3957,11 +4043,105 @@
         <v>34</v>
       </c>
       <c r="S34" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="F35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="N35" s="1" t="s">
         <v>101</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="P35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S35" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="F36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="P36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:D34"/>
+  <autoFilter ref="A3:D36"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/LangMod/EN/Zones.xlsx
+++ b/LangMod/EN/Zones.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Zone" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Zone!$A$3:$D$36</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Zone!$A$3:$D$38</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="136">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -684,6 +684,24 @@
     <t xml:space="preserve">instance_mofuroad</t>
   </si>
   <si>
+    <t xml:space="preserve">instance_music_filth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">演奏会場</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concert Hall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zone_Music_RQX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance_music_noble</t>
+  </si>
+  <si>
     <t xml:space="preserve">instance_guild_merchant</t>
   </si>
   <si>
@@ -835,9 +853,6 @@
   </si>
   <si>
     <t xml:space="preserve">DungeonForest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plain</t>
   </si>
   <si>
     <r>
@@ -1475,7 +1490,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD36"/>
+  <dimension ref="A1:XFD38"/>
   <sheetFormatPr defaultColWidth="14.43359375" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.97"/>
@@ -3350,69 +3365,68 @@
       <c r="R23" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="XDH23" s="0"/>
-      <c r="XDI23" s="0"/>
-      <c r="XDJ23" s="0"/>
-      <c r="XDK23" s="0"/>
-      <c r="XDL23" s="0"/>
-      <c r="XDM23" s="0"/>
-      <c r="XDN23" s="0"/>
-      <c r="XDO23" s="0"/>
-      <c r="XDP23" s="0"/>
-      <c r="XDQ23" s="0"/>
-      <c r="XDR23" s="0"/>
-      <c r="XDS23" s="0"/>
-      <c r="XDT23" s="0"/>
-      <c r="XDU23" s="0"/>
-      <c r="XDV23" s="0"/>
-      <c r="XDW23" s="0"/>
-      <c r="XDX23" s="0"/>
-      <c r="XDY23" s="0"/>
-      <c r="XDZ23" s="0"/>
-      <c r="XEA23" s="0"/>
-      <c r="XEB23" s="0"/>
-      <c r="XEC23" s="0"/>
-      <c r="XED23" s="0"/>
-      <c r="XEE23" s="0"/>
-      <c r="XEF23" s="0"/>
-      <c r="XEG23" s="0"/>
-      <c r="XEH23" s="0"/>
-      <c r="XEI23" s="0"/>
-      <c r="XEJ23" s="0"/>
-      <c r="XEK23" s="0"/>
-      <c r="XEL23" s="0"/>
-      <c r="XEM23" s="0"/>
-      <c r="XEN23" s="0"/>
-      <c r="XEO23" s="0"/>
-      <c r="XEP23" s="0"/>
-      <c r="XEQ23" s="0"/>
-      <c r="XER23" s="0"/>
-      <c r="XES23" s="0"/>
-      <c r="XET23" s="0"/>
-      <c r="XEU23" s="0"/>
-      <c r="XEV23" s="0"/>
-      <c r="XEW23" s="0"/>
-      <c r="XEX23" s="0"/>
-      <c r="XEY23" s="0"/>
-      <c r="XEZ23" s="0"/>
-      <c r="XFA23" s="0"/>
-      <c r="XFB23" s="0"/>
-      <c r="XFC23" s="0"/>
-      <c r="XFD23" s="0"/>
+      <c r="XDH23" s="1"/>
+      <c r="XDI23" s="1"/>
+      <c r="XDJ23" s="1"/>
+      <c r="XDK23" s="1"/>
+      <c r="XDL23" s="1"/>
+      <c r="XDM23" s="1"/>
+      <c r="XDN23" s="1"/>
+      <c r="XDO23" s="1"/>
+      <c r="XDP23" s="1"/>
+      <c r="XDQ23" s="1"/>
+      <c r="XDR23" s="1"/>
+      <c r="XDS23" s="1"/>
+      <c r="XDT23" s="1"/>
+      <c r="XDU23" s="1"/>
+      <c r="XDV23" s="1"/>
+      <c r="XDW23" s="1"/>
+      <c r="XDX23" s="1"/>
+      <c r="XDY23" s="1"/>
+      <c r="XDZ23" s="1"/>
+      <c r="XEA23" s="1"/>
+      <c r="XEB23" s="1"/>
+      <c r="XEC23" s="1"/>
+      <c r="XED23" s="1"/>
+      <c r="XEE23" s="1"/>
+      <c r="XEF23" s="1"/>
+      <c r="XEG23" s="1"/>
+      <c r="XEH23" s="1"/>
+      <c r="XEI23" s="1"/>
+      <c r="XEJ23" s="1"/>
+      <c r="XEK23" s="1"/>
+      <c r="XEL23" s="1"/>
+      <c r="XEM23" s="1"/>
+      <c r="XEN23" s="1"/>
+      <c r="XEO23" s="1"/>
+      <c r="XEP23" s="1"/>
+      <c r="XEQ23" s="1"/>
+      <c r="XER23" s="1"/>
+      <c r="XES23" s="1"/>
+      <c r="XET23" s="1"/>
+      <c r="XEU23" s="1"/>
+      <c r="XEV23" s="1"/>
+      <c r="XEW23" s="1"/>
+      <c r="XEX23" s="1"/>
+      <c r="XEY23" s="1"/>
+      <c r="XEZ23" s="1"/>
+      <c r="XFA23" s="1"/>
+      <c r="XFB23" s="1"/>
+      <c r="XFC23" s="1"/>
+      <c r="XFD23" s="1"/>
     </row>
-    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+    <row r="24" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>1</v>
@@ -3420,20 +3434,15 @@
       <c r="G24" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="H24" s="4"/>
       <c r="I24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4" t="s">
-        <v>77</v>
+      <c r="K24" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4"/>
-      <c r="O24" s="4"/>
+        <v>78</v>
+      </c>
       <c r="P24" s="2" t="n">
         <v>0</v>
       </c>
@@ -3443,25 +3452,68 @@
       <c r="R24" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="S24" s="4"/>
-      <c r="T24" s="4"/>
-      <c r="U24" s="4"/>
-      <c r="V24" s="4"/>
-      <c r="W24" s="4"/>
+      <c r="XDH24" s="1"/>
+      <c r="XDI24" s="1"/>
+      <c r="XDJ24" s="1"/>
+      <c r="XDK24" s="1"/>
+      <c r="XDL24" s="1"/>
+      <c r="XDM24" s="1"/>
+      <c r="XDN24" s="1"/>
+      <c r="XDO24" s="1"/>
+      <c r="XDP24" s="1"/>
+      <c r="XDQ24" s="1"/>
+      <c r="XDR24" s="1"/>
+      <c r="XDS24" s="1"/>
+      <c r="XDT24" s="1"/>
+      <c r="XDU24" s="1"/>
+      <c r="XDV24" s="1"/>
+      <c r="XDW24" s="1"/>
+      <c r="XDX24" s="1"/>
+      <c r="XDY24" s="1"/>
+      <c r="XDZ24" s="1"/>
+      <c r="XEA24" s="1"/>
+      <c r="XEB24" s="1"/>
+      <c r="XEC24" s="1"/>
+      <c r="XED24" s="1"/>
+      <c r="XEE24" s="1"/>
+      <c r="XEF24" s="1"/>
+      <c r="XEG24" s="1"/>
+      <c r="XEH24" s="1"/>
+      <c r="XEI24" s="1"/>
+      <c r="XEJ24" s="1"/>
+      <c r="XEK24" s="1"/>
+      <c r="XEL24" s="1"/>
+      <c r="XEM24" s="1"/>
+      <c r="XEN24" s="1"/>
+      <c r="XEO24" s="1"/>
+      <c r="XEP24" s="1"/>
+      <c r="XEQ24" s="1"/>
+      <c r="XER24" s="1"/>
+      <c r="XES24" s="1"/>
+      <c r="XET24" s="1"/>
+      <c r="XEU24" s="1"/>
+      <c r="XEV24" s="1"/>
+      <c r="XEW24" s="1"/>
+      <c r="XEX24" s="1"/>
+      <c r="XEY24" s="1"/>
+      <c r="XEZ24" s="1"/>
+      <c r="XFA24" s="1"/>
+      <c r="XFB24" s="1"/>
+      <c r="XFC24" s="1"/>
+      <c r="XFD24" s="1"/>
     </row>
-    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="4" t="s">
+    <row r="25" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>80</v>
+      <c r="C25" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>1</v>
@@ -3469,20 +3521,15 @@
       <c r="G25" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="H25" s="4"/>
       <c r="I25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4" t="s">
-        <v>81</v>
+      <c r="K25" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M25" s="4"/>
-      <c r="N25" s="2"/>
-      <c r="O25" s="4"/>
+        <v>78</v>
+      </c>
       <c r="P25" s="2" t="n">
         <v>0</v>
       </c>
@@ -3492,22 +3539,66 @@
       <c r="R25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="S25" s="4"/>
-      <c r="T25" s="4"/>
-      <c r="U25" s="4"/>
-      <c r="V25" s="4"/>
-      <c r="W25" s="4"/>
+      <c r="XDH25" s="1"/>
+      <c r="XDI25" s="1"/>
+      <c r="XDJ25" s="1"/>
+      <c r="XDK25" s="1"/>
+      <c r="XDL25" s="1"/>
+      <c r="XDM25" s="1"/>
+      <c r="XDN25" s="1"/>
+      <c r="XDO25" s="1"/>
+      <c r="XDP25" s="1"/>
+      <c r="XDQ25" s="1"/>
+      <c r="XDR25" s="1"/>
+      <c r="XDS25" s="1"/>
+      <c r="XDT25" s="1"/>
+      <c r="XDU25" s="1"/>
+      <c r="XDV25" s="1"/>
+      <c r="XDW25" s="1"/>
+      <c r="XDX25" s="1"/>
+      <c r="XDY25" s="1"/>
+      <c r="XDZ25" s="1"/>
+      <c r="XEA25" s="1"/>
+      <c r="XEB25" s="1"/>
+      <c r="XEC25" s="1"/>
+      <c r="XED25" s="1"/>
+      <c r="XEE25" s="1"/>
+      <c r="XEF25" s="1"/>
+      <c r="XEG25" s="1"/>
+      <c r="XEH25" s="1"/>
+      <c r="XEI25" s="1"/>
+      <c r="XEJ25" s="1"/>
+      <c r="XEK25" s="1"/>
+      <c r="XEL25" s="1"/>
+      <c r="XEM25" s="1"/>
+      <c r="XEN25" s="1"/>
+      <c r="XEO25" s="1"/>
+      <c r="XEP25" s="1"/>
+      <c r="XEQ25" s="1"/>
+      <c r="XER25" s="1"/>
+      <c r="XES25" s="1"/>
+      <c r="XET25" s="1"/>
+      <c r="XEU25" s="1"/>
+      <c r="XEV25" s="1"/>
+      <c r="XEW25" s="1"/>
+      <c r="XEX25" s="1"/>
+      <c r="XEY25" s="1"/>
+      <c r="XEZ25" s="1"/>
+      <c r="XFA25" s="1"/>
+      <c r="XFB25" s="1"/>
+      <c r="XFC25" s="1"/>
+      <c r="XFD25" s="1"/>
     </row>
-    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="s">
-        <v>82</v>
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>31</v>
@@ -3524,13 +3615,13 @@
       </c>
       <c r="J26" s="4"/>
       <c r="K26" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M26" s="4"/>
-      <c r="N26" s="2"/>
+      <c r="N26" s="4"/>
       <c r="O26" s="4"/>
       <c r="P26" s="2" t="n">
         <v>0</v>
@@ -3547,16 +3638,16 @@
       <c r="V26" s="4"/>
       <c r="W26" s="4"/>
     </row>
-    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>88</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>31</v>
@@ -3567,20 +3658,20 @@
       <c r="G27" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="H27" s="9"/>
+      <c r="H27" s="4"/>
       <c r="I27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9" t="s">
-        <v>89</v>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="M27" s="9"/>
+      <c r="M27" s="4"/>
       <c r="N27" s="2"/>
-      <c r="O27" s="9"/>
+      <c r="O27" s="4"/>
       <c r="P27" s="2" t="n">
         <v>0</v>
       </c>
@@ -3590,24 +3681,25 @@
       <c r="R27" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="S27" s="9"/>
-      <c r="T27" s="9"/>
-      <c r="U27" s="9"/>
-      <c r="V27" s="9"/>
-      <c r="W27" s="9"/>
+      <c r="S27" s="4"/>
+      <c r="T27" s="4"/>
+      <c r="U27" s="4"/>
+      <c r="V27" s="4"/>
+      <c r="W27" s="4"/>
     </row>
-    <row r="28" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="E28" s="5" t="s">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>1</v>
@@ -3615,15 +3707,20 @@
       <c r="G28" s="2" t="n">
         <v>100</v>
       </c>
+      <c r="H28" s="4"/>
       <c r="I28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K28" s="6" t="s">
-        <v>93</v>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="M28" s="4"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="4"/>
       <c r="P28" s="2" t="n">
         <v>0</v>
       </c>
@@ -3633,68 +3730,25 @@
       <c r="R28" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="XDH28" s="1"/>
-      <c r="XDI28" s="1"/>
-      <c r="XDJ28" s="1"/>
-      <c r="XDK28" s="1"/>
-      <c r="XDL28" s="1"/>
-      <c r="XDM28" s="1"/>
-      <c r="XDN28" s="1"/>
-      <c r="XDO28" s="1"/>
-      <c r="XDP28" s="1"/>
-      <c r="XDQ28" s="1"/>
-      <c r="XDR28" s="1"/>
-      <c r="XDS28" s="1"/>
-      <c r="XDT28" s="1"/>
-      <c r="XDU28" s="1"/>
-      <c r="XDV28" s="1"/>
-      <c r="XDW28" s="1"/>
-      <c r="XDX28" s="1"/>
-      <c r="XDY28" s="1"/>
-      <c r="XDZ28" s="1"/>
-      <c r="XEA28" s="1"/>
-      <c r="XEB28" s="1"/>
-      <c r="XEC28" s="1"/>
-      <c r="XED28" s="1"/>
-      <c r="XEE28" s="1"/>
-      <c r="XEF28" s="1"/>
-      <c r="XEG28" s="1"/>
-      <c r="XEH28" s="1"/>
-      <c r="XEI28" s="1"/>
-      <c r="XEJ28" s="1"/>
-      <c r="XEK28" s="1"/>
-      <c r="XEL28" s="1"/>
-      <c r="XEM28" s="1"/>
-      <c r="XEN28" s="1"/>
-      <c r="XEO28" s="1"/>
-      <c r="XEP28" s="1"/>
-      <c r="XEQ28" s="1"/>
-      <c r="XER28" s="1"/>
-      <c r="XES28" s="1"/>
-      <c r="XET28" s="1"/>
-      <c r="XEU28" s="1"/>
-      <c r="XEV28" s="1"/>
-      <c r="XEW28" s="1"/>
-      <c r="XEX28" s="1"/>
-      <c r="XEY28" s="1"/>
-      <c r="XEZ28" s="1"/>
-      <c r="XFA28" s="1"/>
-      <c r="XFB28" s="1"/>
-      <c r="XFC28" s="1"/>
-      <c r="XFD28" s="1"/>
+      <c r="S28" s="4"/>
+      <c r="T28" s="4"/>
+      <c r="U28" s="4"/>
+      <c r="V28" s="4"/>
+      <c r="W28" s="4"/>
     </row>
-    <row r="29" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
+    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="E29" s="5" t="s">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>1</v>
@@ -3702,15 +3756,20 @@
       <c r="G29" s="2" t="n">
         <v>100</v>
       </c>
+      <c r="H29" s="9"/>
       <c r="I29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K29" s="6" t="s">
+      <c r="J29" s="9"/>
+      <c r="K29" s="9" t="s">
         <v>95</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="M29" s="9"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="9"/>
       <c r="P29" s="2" t="n">
         <v>0</v>
       </c>
@@ -3720,68 +3779,24 @@
       <c r="R29" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="XDH29" s="1"/>
-      <c r="XDI29" s="1"/>
-      <c r="XDJ29" s="1"/>
-      <c r="XDK29" s="1"/>
-      <c r="XDL29" s="1"/>
-      <c r="XDM29" s="1"/>
-      <c r="XDN29" s="1"/>
-      <c r="XDO29" s="1"/>
-      <c r="XDP29" s="1"/>
-      <c r="XDQ29" s="1"/>
-      <c r="XDR29" s="1"/>
-      <c r="XDS29" s="1"/>
-      <c r="XDT29" s="1"/>
-      <c r="XDU29" s="1"/>
-      <c r="XDV29" s="1"/>
-      <c r="XDW29" s="1"/>
-      <c r="XDX29" s="1"/>
-      <c r="XDY29" s="1"/>
-      <c r="XDZ29" s="1"/>
-      <c r="XEA29" s="1"/>
-      <c r="XEB29" s="1"/>
-      <c r="XEC29" s="1"/>
-      <c r="XED29" s="1"/>
-      <c r="XEE29" s="1"/>
-      <c r="XEF29" s="1"/>
-      <c r="XEG29" s="1"/>
-      <c r="XEH29" s="1"/>
-      <c r="XEI29" s="1"/>
-      <c r="XEJ29" s="1"/>
-      <c r="XEK29" s="1"/>
-      <c r="XEL29" s="1"/>
-      <c r="XEM29" s="1"/>
-      <c r="XEN29" s="1"/>
-      <c r="XEO29" s="1"/>
-      <c r="XEP29" s="1"/>
-      <c r="XEQ29" s="1"/>
-      <c r="XER29" s="1"/>
-      <c r="XES29" s="1"/>
-      <c r="XET29" s="1"/>
-      <c r="XEU29" s="1"/>
-      <c r="XEV29" s="1"/>
-      <c r="XEW29" s="1"/>
-      <c r="XEX29" s="1"/>
-      <c r="XEY29" s="1"/>
-      <c r="XEZ29" s="1"/>
-      <c r="XFA29" s="1"/>
-      <c r="XFB29" s="1"/>
-      <c r="XFC29" s="1"/>
-      <c r="XFD29" s="1"/>
+      <c r="S29" s="9"/>
+      <c r="T29" s="9"/>
+      <c r="U29" s="9"/>
+      <c r="V29" s="9"/>
+      <c r="W29" s="9"/>
     </row>
     <row r="30" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>1</v>
@@ -3793,12 +3808,11 @@
         <v>0</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O30" s="1"/>
       <c r="P30" s="2" t="n">
         <v>0</v>
       </c>
@@ -3858,112 +3872,193 @@
       <c r="XFC30" s="1"/>
       <c r="XFD30" s="1"/>
     </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
+    <row r="31" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E31" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F31" s="1" t="n">
+      <c r="F31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="I31" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L31" s="1" t="s">
+      <c r="I31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="L31" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N31" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="O31" s="2" t="s">
+      <c r="P31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="XDH31" s="1"/>
+      <c r="XDI31" s="1"/>
+      <c r="XDJ31" s="1"/>
+      <c r="XDK31" s="1"/>
+      <c r="XDL31" s="1"/>
+      <c r="XDM31" s="1"/>
+      <c r="XDN31" s="1"/>
+      <c r="XDO31" s="1"/>
+      <c r="XDP31" s="1"/>
+      <c r="XDQ31" s="1"/>
+      <c r="XDR31" s="1"/>
+      <c r="XDS31" s="1"/>
+      <c r="XDT31" s="1"/>
+      <c r="XDU31" s="1"/>
+      <c r="XDV31" s="1"/>
+      <c r="XDW31" s="1"/>
+      <c r="XDX31" s="1"/>
+      <c r="XDY31" s="1"/>
+      <c r="XDZ31" s="1"/>
+      <c r="XEA31" s="1"/>
+      <c r="XEB31" s="1"/>
+      <c r="XEC31" s="1"/>
+      <c r="XED31" s="1"/>
+      <c r="XEE31" s="1"/>
+      <c r="XEF31" s="1"/>
+      <c r="XEG31" s="1"/>
+      <c r="XEH31" s="1"/>
+      <c r="XEI31" s="1"/>
+      <c r="XEJ31" s="1"/>
+      <c r="XEK31" s="1"/>
+      <c r="XEL31" s="1"/>
+      <c r="XEM31" s="1"/>
+      <c r="XEN31" s="1"/>
+      <c r="XEO31" s="1"/>
+      <c r="XEP31" s="1"/>
+      <c r="XEQ31" s="1"/>
+      <c r="XER31" s="1"/>
+      <c r="XES31" s="1"/>
+      <c r="XET31" s="1"/>
+      <c r="XEU31" s="1"/>
+      <c r="XEV31" s="1"/>
+      <c r="XEW31" s="1"/>
+      <c r="XEX31" s="1"/>
+      <c r="XEY31" s="1"/>
+      <c r="XEZ31" s="1"/>
+      <c r="XFA31" s="1"/>
+      <c r="XFB31" s="1"/>
+      <c r="XFC31" s="1"/>
+      <c r="XFD31" s="1"/>
+    </row>
+    <row r="32" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="P31" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S31" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="F32" s="1" t="n">
+      <c r="C32" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="I32" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="P32" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="1" t="s">
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O32" s="1"/>
+      <c r="P32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="S32" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="XDH32" s="1"/>
+      <c r="XDI32" s="1"/>
+      <c r="XDJ32" s="1"/>
+      <c r="XDK32" s="1"/>
+      <c r="XDL32" s="1"/>
+      <c r="XDM32" s="1"/>
+      <c r="XDN32" s="1"/>
+      <c r="XDO32" s="1"/>
+      <c r="XDP32" s="1"/>
+      <c r="XDQ32" s="1"/>
+      <c r="XDR32" s="1"/>
+      <c r="XDS32" s="1"/>
+      <c r="XDT32" s="1"/>
+      <c r="XDU32" s="1"/>
+      <c r="XDV32" s="1"/>
+      <c r="XDW32" s="1"/>
+      <c r="XDX32" s="1"/>
+      <c r="XDY32" s="1"/>
+      <c r="XDZ32" s="1"/>
+      <c r="XEA32" s="1"/>
+      <c r="XEB32" s="1"/>
+      <c r="XEC32" s="1"/>
+      <c r="XED32" s="1"/>
+      <c r="XEE32" s="1"/>
+      <c r="XEF32" s="1"/>
+      <c r="XEG32" s="1"/>
+      <c r="XEH32" s="1"/>
+      <c r="XEI32" s="1"/>
+      <c r="XEJ32" s="1"/>
+      <c r="XEK32" s="1"/>
+      <c r="XEL32" s="1"/>
+      <c r="XEM32" s="1"/>
+      <c r="XEN32" s="1"/>
+      <c r="XEO32" s="1"/>
+      <c r="XEP32" s="1"/>
+      <c r="XEQ32" s="1"/>
+      <c r="XER32" s="1"/>
+      <c r="XES32" s="1"/>
+      <c r="XET32" s="1"/>
+      <c r="XEU32" s="1"/>
+      <c r="XEV32" s="1"/>
+      <c r="XEW32" s="1"/>
+      <c r="XEX32" s="1"/>
+      <c r="XEY32" s="1"/>
+      <c r="XEZ32" s="1"/>
+      <c r="XFA32" s="1"/>
+      <c r="XFB32" s="1"/>
+      <c r="XFC32" s="1"/>
+      <c r="XFD32" s="1"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="s">
-        <v>110</v>
+      <c r="A33" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>1</v>
@@ -3975,16 +4070,16 @@
         <v>0</v>
       </c>
       <c r="J33" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="O33" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="O33" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="P33" s="1" t="n">
         <v>0</v>
@@ -3996,21 +4091,21 @@
         <v>34</v>
       </c>
       <c r="S33" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>113</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>1</v>
@@ -4022,16 +4117,16 @@
         <v>0</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="P34" s="1" t="n">
         <v>0</v>
@@ -4043,21 +4138,21 @@
         <v>34</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>122</v>
+        <v>117</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>1</v>
@@ -4069,16 +4164,16 @@
         <v>0</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="P35" s="1" t="n">
         <v>0</v>
@@ -4090,21 +4185,21 @@
         <v>34</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>128</v>
+        <v>122</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>1</v>
@@ -4116,16 +4211,16 @@
         <v>0</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="P36" s="1" t="n">
         <v>0</v>
@@ -4137,11 +4232,105 @@
         <v>34</v>
       </c>
       <c r="S36" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="P37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S37" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="F38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="P38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S38" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:D36"/>
+  <autoFilter ref="A3:D38"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
